--- a/JsonConverter/ExcelFiles/Ship.xlsx
+++ b/JsonConverter/ExcelFiles/Ship.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
   <si>
     <t xml:space="preserve">고유 ID</t>
   </si>
@@ -28,7 +28,10 @@
     <t xml:space="preserve">설명 (도감용)</t>
   </si>
   <si>
-    <t xml:space="preserve">적의 체력</t>
+    <t xml:space="preserve">체력</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화물칸</t>
   </si>
   <si>
     <t xml:space="preserve">프리팹으로 구현</t>
@@ -43,6 +46,9 @@
     <t xml:space="preserve">float</t>
   </si>
   <si>
+    <t xml:space="preserve">int</t>
+  </si>
+  <si>
     <t xml:space="preserve">Id</t>
   </si>
   <si>
@@ -53,6 +59,9 @@
   </si>
   <si>
     <t xml:space="preserve">Max_HP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cargo</t>
   </si>
   <si>
     <t xml:space="preserve">PrefabPath</t>
@@ -503,6 +512,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -513,10 +526,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -773,18 +782,19 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S1000"/>
+  <dimension ref="A1:T1000"/>
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.93"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="35.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="24.35"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="7" style="1" width="11.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16380" min="20" style="1" width="11.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16381" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="6.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="35.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="24.35"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16" min="8" style="1" width="11.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16381" min="21" style="1" width="11.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16382" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -798,519 +808,576 @@
       <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
     </row>
     <row r="3" s="7" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="6"/>
-      <c r="P3" s="0"/>
-      <c r="Q3" s="0"/>
-      <c r="R3" s="0"/>
-      <c r="S3" s="0"/>
+        <v>12</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="6"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="E4" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
+      <c r="E4" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="D5" s="10" t="n">
         <v>200</v>
       </c>
-      <c r="E5" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
+      <c r="E5" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D6" s="10" t="n">
         <v>500</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
+      <c r="E6" s="10" t="n">
+        <v>500</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="D7" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
+      <c r="E7" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="D8" s="10" t="n">
         <v>200</v>
       </c>
-      <c r="E8" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
+      <c r="E8" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="11"/>
+      <c r="P8" s="11"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="D9" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="E9" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
+      <c r="E9" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="D10" s="10" t="n">
         <v>400</v>
       </c>
-      <c r="E10" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
+      <c r="E10" s="10" t="n">
+        <v>400</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="11"/>
+      <c r="P10" s="11"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="D11" s="10" t="n">
         <v>500</v>
       </c>
-      <c r="E11" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
+      <c r="E11" s="10" t="n">
+        <v>500</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="9"/>
+      <c r="D12" s="10"/>
       <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="9"/>
+      <c r="D13" s="10"/>
       <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="12"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="12"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
+      <c r="A30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
+      <c r="A32" s="11"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
+      <c r="A33" s="11"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="2"/>
+      <c r="A34" s="11"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="2"/>
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
     </row>
     <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
     </row>
     <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
     </row>
     <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
     </row>
     <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
     </row>
     <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
     </row>
     <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
     </row>
     <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
     </row>
     <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/JsonConverter/ExcelFiles/Ship.xlsx
+++ b/JsonConverter/ExcelFiles/Ship.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="59">
   <si>
     <t xml:space="preserve">고유 ID</t>
   </si>
@@ -34,9 +34,15 @@
     <t xml:space="preserve">화물칸</t>
   </si>
   <si>
+    <t xml:space="preserve">가격</t>
+  </si>
+  <si>
     <t xml:space="preserve">프리팹으로 구현</t>
   </si>
   <si>
+    <t xml:space="preserve">이미지</t>
+  </si>
+  <si>
     <t xml:space="preserve">(name)</t>
   </si>
   <si>
@@ -64,7 +70,13 @@
     <t xml:space="preserve">Cargo</t>
   </si>
   <si>
+    <t xml:space="preserve">Price</t>
+  </si>
+  <si>
     <t xml:space="preserve">PrefabPath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IconPath</t>
   </si>
   <si>
     <t xml:space="preserve">ship_0001</t>
@@ -117,6 +129,28 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">Icon/Ship/s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">hip_0001</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">ship_0002</t>
   </si>
   <si>
@@ -148,6 +182,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">Icon/Ship/ship_0002</t>
+  </si>
+  <si>
     <t xml:space="preserve">ship_0003</t>
   </si>
   <si>
@@ -179,6 +216,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">Icon/Ship/ship_0003</t>
+  </si>
+  <si>
     <t xml:space="preserve">ship_0004</t>
   </si>
   <si>
@@ -210,6 +250,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">Icon/Ship/ship_0004</t>
+  </si>
+  <si>
     <t xml:space="preserve">ship_0005</t>
   </si>
   <si>
@@ -241,6 +284,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">Icon/Ship/ship_0005</t>
+  </si>
+  <si>
     <t xml:space="preserve">ship_0006</t>
   </si>
   <si>
@@ -272,6 +318,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">Icon/Ship/ship_0006</t>
+  </si>
+  <si>
     <t xml:space="preserve">ship_0007</t>
   </si>
   <si>
@@ -303,6 +352,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">Icon/Ship/ship_0007</t>
+  </si>
+  <si>
     <t xml:space="preserve">ship_0008</t>
   </si>
   <si>
@@ -333,6 +385,9 @@
       <t xml:space="preserve">ship_0008</t>
     </r>
   </si>
+  <si>
+    <t xml:space="preserve">Icon/Ship/ship_0008</t>
+  </si>
 </sst>
 </file>
 
@@ -342,7 +397,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -383,6 +438,13 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="&quot;맑은 고딕&quot;"/>
+      <family val="0"/>
+      <charset val="129"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF008000"/>
       <name val="&quot;맑은 고딕&quot;"/>
@@ -406,7 +468,7 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="&quot;맑은 고딕&quot;"/>
+      <name val="Arial"/>
       <family val="0"/>
       <charset val="129"/>
     </font>
@@ -479,7 +541,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -496,15 +558,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -516,16 +586,16 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -782,7 +852,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:T1000"/>
+  <dimension ref="A1:U1000"/>
   <sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.84"/>
@@ -790,11 +860,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.93"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="6.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="35.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="24.35"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16" min="8" style="1" width="11.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16381" min="21" style="1" width="11.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16382" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="35.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="24.35"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="17" min="9" style="1" width="11.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16382" min="22" style="1" width="11.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -811,573 +881,653 @@
       <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" s="7" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="H2" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="B3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="C3" s="5" t="s">
         <v>13</v>
       </c>
+      <c r="D3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="F3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="6"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
+        <v>16</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="F4" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
+      <c r="F4" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="12"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="D5" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E5" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="F5" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
+      <c r="F5" s="11" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="D6" s="11" t="n">
         <v>500</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="11" t="n">
         <v>500</v>
       </c>
-      <c r="F6" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
+      <c r="F6" s="11" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="D7" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="F7" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="11"/>
+      <c r="F7" s="11" t="n">
+        <v>999999</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="12"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="D8" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="F8" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
+      <c r="F8" s="11" t="n">
+        <v>999999</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="D9" s="11" t="n">
         <v>300</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="11" t="n">
         <v>300</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
+      <c r="F9" s="11" t="n">
+        <v>999999</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="10" t="n">
+        <v>51</v>
+      </c>
+      <c r="D10" s="11" t="n">
         <v>400</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="11" t="n">
         <v>400</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
+      <c r="F10" s="11" t="n">
+        <v>999999</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="D11" s="11" t="n">
         <v>500</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E11" s="11" t="n">
         <v>500</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
+      <c r="F11" s="11" t="n">
+        <v>999999</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="12"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="12"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="12"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="12"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="12"/>
+      <c r="Q15" s="12"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
+      <c r="A19" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="11"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
+      <c r="A25" s="12"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="11"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
+      <c r="A27" s="12"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
       <c r="F27" s="12"/>
+      <c r="G27" s="14"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="11"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="11"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="11"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="11"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
+      <c r="A31" s="12"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
+      <c r="A33" s="12"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="2"/>
+      <c r="A34" s="12"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="13"/>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="2"/>
+      <c r="A35" s="12"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="13"/>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F36" s="2"/>
+      <c r="G36" s="13"/>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F37" s="2"/>
+      <c r="G37" s="13"/>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F38" s="2"/>
+      <c r="G38" s="13"/>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F39" s="2"/>
+      <c r="G39" s="13"/>
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F40" s="2"/>
+      <c r="G40" s="13"/>
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F41" s="2"/>
+      <c r="G41" s="13"/>
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F42" s="2"/>
+      <c r="G42" s="13"/>
     </row>
     <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F43" s="2"/>
+      <c r="G43" s="13"/>
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F45" s="2"/>
+      <c r="G45" s="13"/>
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F46" s="2"/>
+      <c r="G46" s="13"/>
     </row>
     <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F47" s="2"/>
+      <c r="G47" s="13"/>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F48" s="2"/>
+      <c r="G48" s="13"/>
     </row>
     <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F49" s="2"/>
+      <c r="G49" s="13"/>
     </row>
     <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F50" s="2"/>
+      <c r="G50" s="13"/>
     </row>
     <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F51" s="2"/>
+      <c r="G51" s="13"/>
     </row>
     <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F52" s="2"/>
+      <c r="G52" s="13"/>
     </row>
     <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F53" s="2"/>
+      <c r="G53" s="13"/>
     </row>
     <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F54" s="2"/>
+      <c r="G54" s="13"/>
     </row>
     <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
